--- a/project_tracker/Project_Tracker_v2.xlsx
+++ b/project_tracker/Project_Tracker_v2.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="721">
   <si>
     <t xml:space="preserve">Project tracker: ED305 digital twin, SCooP, dual-link, semantic comm</t>
   </si>
@@ -182,6 +182,27 @@
   </si>
   <si>
     <t xml:space="preserve">Owner = role. Put each person's name against the role in Lists; Tasks and Gantt show it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Sheets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload the .xlsx to Google Drive -&gt; open it -&gt; File &gt; Save as Google Sheets. Share the Google Sheet (Editor) with the team; use only that copy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nobody downloads, edits offline and re-uploads: that overwrites everyone else's changes. File &gt; Version history shows who changed what.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropdown values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stored in each column's rule (Data &gt; Data validation). To add a status/role/goal: add it there; also add a new role to Lists so Person can be looked up.</t>
   </si>
   <si>
     <t xml:space="preserve">All numbers are formulas over Tasks, Problems and Interfaces.</t>
@@ -2389,7 +2410,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFDECEA"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -2424,8 +2445,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDECEA"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFF4B6B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -2645,7 +2666,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2763,18 +2784,18 @@
     <dxf>
       <font>
         <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFC00000"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -2817,24 +2838,6 @@
           <bgColor rgb="FFA6A6A6"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDECEA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="false" diagonalDown="false">
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2889,7 +2892,7 @@
       <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FFF4B6B6"/>
-      <rgbColor rgb="FFFDECEA"/>
+      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -3100,7 +3103,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -3261,6 +3264,40 @@
       </c>
       <c r="B23" s="4" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6"/>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3294,44 +3331,44 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="8" t="n">
         <f aca="false">COUNTIFS(Tasks!$B$4:$B$403,$A5,Tasks!$H$4:$H$403,"Not Started")</f>
@@ -3372,7 +3409,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="8" t="n">
         <f aca="false">COUNTIFS(Tasks!$B$4:$B$403,$A6,Tasks!$H$4:$H$403,"Not Started")</f>
@@ -3413,7 +3450,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">COUNTIFS(Tasks!$B$4:$B$403,$A7,Tasks!$H$4:$H$403,"Not Started")</f>
@@ -3454,7 +3491,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">COUNTIFS(Tasks!$B$4:$B$403,$A8,Tasks!$H$4:$H$403,"Not Started")</f>
@@ -3495,7 +3532,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">COUNTIFS(Tasks!$B$4:$B$403,$A9,Tasks!$H$4:$H$403,"Not Started")</f>
@@ -3536,7 +3573,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">SUM(B5:B9)</f>
@@ -3577,42 +3614,42 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A14,Lists!$A$4:$A$12,0)),"")</f>
@@ -3657,7 +3694,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A15,Lists!$A$4:$A$12,0)),"")</f>
@@ -3702,7 +3739,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A16,Lists!$A$4:$A$12,0)),"")</f>
@@ -3747,7 +3784,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A17,Lists!$A$4:$A$12,0)),"")</f>
@@ -3792,7 +3829,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A18,Lists!$A$4:$A$12,0)),"")</f>
@@ -3837,7 +3874,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A19,Lists!$A$4:$A$12,0)),"")</f>
@@ -3882,7 +3919,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A20,Lists!$A$4:$A$12,0)),"")</f>
@@ -3927,7 +3964,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A21,Lists!$A$4:$A$12,0)),"")</f>
@@ -3972,7 +4009,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="str">
         <f aca="false">IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($A22,Lists!$A$4:$A$12,0)),"")</f>
@@ -4017,7 +4054,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C23" s="5" t="n">
         <f aca="false">SUM(C14:C22)</f>
@@ -4061,24 +4098,24 @@
         <v>7</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B27" s="8" t="n">
         <f aca="false">COUNTIFS(Problems!$F$4:$F$203,$A27,Problems!$G$4:$G$203,"Open")</f>
@@ -4103,7 +4140,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B28" s="8" t="n">
         <f aca="false">COUNTIFS(Problems!$F$4:$F$203,$A28,Problems!$G$4:$G$203,"Open")</f>
@@ -4128,7 +4165,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B29" s="8" t="n">
         <f aca="false">COUNTIFS(Problems!$F$4:$F$203,$A29,Problems!$G$4:$G$203,"Open")</f>
@@ -4156,12 +4193,12 @@
         <v>9</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B33" s="8" t="n">
         <f aca="false">COUNTIF(Interfaces!$J$4:$J$103,$A33)</f>
@@ -4170,7 +4207,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B34" s="8" t="n">
         <f aca="false">COUNTIF(Interfaces!$J$4:$J$103,$A34)</f>
@@ -4179,7 +4216,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B35" s="8" t="n">
         <f aca="false">COUNTIF(Interfaces!$J$4:$J$103,$A35)</f>
@@ -4188,7 +4225,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B36" s="8" t="n">
         <f aca="false">COUNTIF(Interfaces!$J$4:$J$103,$A36)</f>
@@ -4239,84 +4276,84 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G4" s="13" t="str">
         <f aca="false">IF($F4="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F4,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I4" s="14" t="n">
         <v>46307</v>
@@ -4330,7 +4367,7 @@
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="4"/>
@@ -4338,29 +4375,29 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G5" s="13" t="str">
         <f aca="false">IF($F5="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F5,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I5" s="14" t="n">
         <v>46195</v>
@@ -4374,39 +4411,39 @@
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N5" s="12"/>
       <c r="O5" s="4"/>
       <c r="P5" s="12" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G6" s="13" t="str">
         <f aca="false">IF($F6="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F6,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I6" s="14" t="n">
         <v>46195</v>
@@ -4423,27 +4460,27 @@
       <c r="N6" s="12"/>
       <c r="O6" s="4"/>
       <c r="P6" s="12" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G7" s="13" t="str">
         <f aca="false">IF($F7="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F7,Lists!$A$4:$A$12,0)),""))</f>
@@ -4460,30 +4497,30 @@
       <c r="M7" s="4"/>
       <c r="N7" s="12"/>
       <c r="O7" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G8" s="13" t="str">
         <f aca="false">IF($F8="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F8,Lists!$A$4:$A$12,0)),""))</f>
@@ -4500,30 +4537,30 @@
       <c r="M8" s="4"/>
       <c r="N8" s="12"/>
       <c r="O8" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G9" s="13" t="str">
         <f aca="false">IF($F9="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F9,Lists!$A$4:$A$12,0)),""))</f>
@@ -4540,30 +4577,30 @@
       <c r="M9" s="4"/>
       <c r="N9" s="12"/>
       <c r="O9" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="F10" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G10" s="13" t="str">
         <f aca="false">IF($F10="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F10,Lists!$A$4:$A$12,0)),""))</f>
@@ -4580,30 +4617,30 @@
       <c r="M10" s="4"/>
       <c r="N10" s="12"/>
       <c r="O10" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G11" s="13" t="str">
         <f aca="false">IF($F11="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F11,Lists!$A$4:$A$12,0)),""))</f>
@@ -4620,37 +4657,37 @@
       <c r="M11" s="4"/>
       <c r="N11" s="12"/>
       <c r="O11" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G12" s="13" t="str">
         <f aca="false">IF($F12="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F12,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I12" s="14" t="n">
         <v>46202</v>
@@ -4664,39 +4701,39 @@
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="4"/>
       <c r="P12" s="12" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G13" s="13" t="str">
         <f aca="false">IF($F13="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F13,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I13" s="14" t="n">
         <v>46307</v>
@@ -4710,7 +4747,7 @@
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N13" s="12"/>
       <c r="O13" s="4"/>
@@ -4718,29 +4755,29 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G14" s="13" t="str">
         <f aca="false">IF($F14="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F14,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I14" s="14" t="n">
         <v>46307</v>
@@ -4753,10 +4790,10 @@
         <v>46318</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N14" s="12"/>
       <c r="O14" s="4"/>
@@ -4764,29 +4801,29 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G15" s="13" t="str">
         <f aca="false">IF($F15="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F15,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>46314</v>
@@ -4799,44 +4836,44 @@
         <v>46353</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="N15" s="12"/>
       <c r="O15" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G16" s="13" t="str">
         <f aca="false">IF($F16="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F16,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I16" s="14" t="n">
         <v>46202</v>
@@ -4852,37 +4889,37 @@
       <c r="M16" s="4"/>
       <c r="N16" s="12"/>
       <c r="O16" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G17" s="13" t="str">
         <f aca="false">IF($F17="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F17,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="12"/>
@@ -4894,37 +4931,37 @@
       <c r="M17" s="4"/>
       <c r="N17" s="12"/>
       <c r="O17" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G18" s="13" t="str">
         <f aca="false">IF($F18="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F18,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I18" s="14" t="n">
         <v>46321</v>
@@ -4937,7 +4974,7 @@
         <v>46346</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="12"/>
@@ -4946,22 +4983,22 @@
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G19" s="13" t="str">
         <f aca="false">IF($F19="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F19,Lists!$A$4:$A$12,0)),""))</f>
@@ -4982,30 +5019,30 @@
       <c r="M19" s="4"/>
       <c r="N19" s="12"/>
       <c r="O19" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G20" s="13" t="str">
         <f aca="false">IF($F20="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F20,Lists!$A$4:$A$12,0)),""))</f>
@@ -5026,37 +5063,37 @@
       <c r="M20" s="4"/>
       <c r="N20" s="12"/>
       <c r="O20" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G21" s="13" t="str">
         <f aca="false">IF($F21="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F21,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I21" s="14" t="n">
         <v>46307</v>
@@ -5070,41 +5107,41 @@
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="4" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G22" s="13" t="str">
         <f aca="false">IF($F22="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F22,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I22" s="14" t="n">
         <v>46202</v>
@@ -5121,34 +5158,34 @@
       <c r="N22" s="12"/>
       <c r="O22" s="4"/>
       <c r="P22" s="12" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G23" s="13" t="str">
         <f aca="false">IF($F23="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F23,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>46202</v>
@@ -5165,34 +5202,34 @@
       <c r="N23" s="12"/>
       <c r="O23" s="4"/>
       <c r="P23" s="12" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G24" s="13" t="str">
         <f aca="false">IF($F24="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F24,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I24" s="14" t="n">
         <v>46307</v>
@@ -5206,39 +5243,39 @@
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="P24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G25" s="13" t="str">
         <f aca="false">IF($F25="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F25,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>46202</v>
@@ -5255,34 +5292,34 @@
       <c r="N25" s="12"/>
       <c r="O25" s="4"/>
       <c r="P25" s="12" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G26" s="13" t="str">
         <f aca="false">IF($F26="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F26,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I26" s="14" t="n">
         <v>46209</v>
@@ -5298,37 +5335,37 @@
       <c r="M26" s="4"/>
       <c r="N26" s="12"/>
       <c r="O26" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G27" s="13" t="str">
         <f aca="false">IF($F27="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F27,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I27" s="14" t="n">
         <v>46307</v>
@@ -5341,42 +5378,42 @@
         <v>46346</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="N27" s="12"/>
       <c r="O27" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="P27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G28" s="13" t="str">
         <f aca="false">IF($F28="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F28,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I28" s="14" t="n">
         <v>46342</v>
@@ -5389,10 +5426,10 @@
         <v>46360</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="N28" s="12"/>
       <c r="O28" s="4"/>
@@ -5400,29 +5437,29 @@
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G29" s="13" t="str">
         <f aca="false">IF($F29="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F29,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I29" s="14" t="n">
         <v>46335</v>
@@ -5435,42 +5472,42 @@
         <v>46381</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="N29" s="12"/>
       <c r="O29" s="4"/>
       <c r="P29" s="12" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G30" s="13" t="str">
         <f aca="false">IF($F30="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F30,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="12"/>
@@ -5482,37 +5519,37 @@
       <c r="M30" s="4"/>
       <c r="N30" s="12"/>
       <c r="O30" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G31" s="13" t="str">
         <f aca="false">IF($F31="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F31,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I31" s="14" t="n">
         <v>46349</v>
@@ -5525,10 +5562,10 @@
         <v>46381</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="N31" s="12"/>
       <c r="O31" s="4"/>
@@ -5536,29 +5573,29 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G32" s="13" t="str">
         <f aca="false">IF($F32="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F32,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I32" s="14" t="n">
         <v>46384</v>
@@ -5571,44 +5608,44 @@
         <v>46416</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="N32" s="12"/>
       <c r="O32" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G33" s="13" t="str">
         <f aca="false">IF($F33="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F33,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="12"/>
@@ -5620,37 +5657,37 @@
       <c r="M33" s="4"/>
       <c r="N33" s="12"/>
       <c r="O33" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G34" s="13" t="str">
         <f aca="false">IF($F34="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F34,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I34" s="14" t="n">
         <v>46384</v>
@@ -5670,27 +5707,27 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G35" s="13" t="str">
         <f aca="false">IF($F35="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F35,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I35" s="14" t="n">
         <v>46398</v>
@@ -5710,29 +5747,29 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G36" s="13" t="str">
         <f aca="false">IF($F36="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F36,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I36" s="14" t="n">
         <v>46314</v>
@@ -5745,7 +5782,7 @@
         <v>46332</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M36" s="4"/>
       <c r="N36" s="12"/>
@@ -5754,29 +5791,29 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G37" s="13" t="str">
         <f aca="false">IF($F37="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F37,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I37" s="14" t="n">
         <v>46342</v>
@@ -5789,7 +5826,7 @@
         <v>46360</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="M37" s="4"/>
       <c r="N37" s="12"/>
@@ -5798,29 +5835,29 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G38" s="13" t="str">
         <f aca="false">IF($F38="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F38,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I38" s="14" t="n">
         <v>46363</v>
@@ -5833,7 +5870,7 @@
         <v>46381</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="M38" s="4"/>
       <c r="N38" s="12"/>
@@ -5842,29 +5879,29 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G39" s="13" t="str">
         <f aca="false">IF($F39="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F39,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I39" s="14" t="n">
         <v>46363</v>
@@ -5877,7 +5914,7 @@
         <v>46395</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="M39" s="4"/>
       <c r="N39" s="12"/>
@@ -5886,29 +5923,29 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G40" s="13" t="str">
         <f aca="false">IF($F40="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F40,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I40" s="14" t="n">
         <v>46363</v>
@@ -5921,7 +5958,7 @@
         <v>46395</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M40" s="4"/>
       <c r="N40" s="12"/>
@@ -5930,29 +5967,29 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G41" s="13" t="str">
         <f aca="false">IF($F41="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F41,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I41" s="14" t="n">
         <v>46398</v>
@@ -5965,7 +6002,7 @@
         <v>46409</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="M41" s="4"/>
       <c r="N41" s="12"/>
@@ -5974,29 +6011,29 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G42" s="13" t="str">
         <f aca="false">IF($F42="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F42,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I42" s="14" t="n">
         <v>46398</v>
@@ -6009,7 +6046,7 @@
         <v>46423</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M42" s="4"/>
       <c r="N42" s="12"/>
@@ -6018,27 +6055,27 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G43" s="13" t="str">
         <f aca="false">IF($F43="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F43,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I43" s="14" t="n">
         <v>46426</v>
@@ -6051,7 +6088,7 @@
         <v>46430</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="M43" s="4"/>
       <c r="N43" s="12"/>
@@ -6060,29 +6097,29 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G44" s="13" t="str">
         <f aca="false">IF($F44="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F44,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I44" s="14" t="n">
         <v>46307</v>
@@ -6095,7 +6132,7 @@
         <v>46318</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M44" s="4"/>
       <c r="N44" s="12"/>
@@ -6104,29 +6141,29 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G45" s="13" t="str">
         <f aca="false">IF($F45="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F45,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I45" s="14" t="n">
         <v>46314</v>
@@ -6139,10 +6176,10 @@
         <v>46339</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="N45" s="12"/>
       <c r="O45" s="4"/>
@@ -6150,29 +6187,29 @@
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G46" s="13" t="str">
         <f aca="false">IF($F46="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F46,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I46" s="14" t="n">
         <v>46307</v>
@@ -6186,39 +6223,39 @@
       </c>
       <c r="L46" s="12"/>
       <c r="M46" s="4" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="N46" s="12"/>
       <c r="O46" s="4" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G47" s="13" t="str">
         <f aca="false">IF($F47="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F47,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I47" s="14" t="n">
         <v>46321</v>
@@ -6231,42 +6268,42 @@
         <v>46339</v>
       </c>
       <c r="L47" s="12" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="N47" s="12" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="O47" s="4"/>
       <c r="P47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G48" s="13" t="str">
         <f aca="false">IF($F48="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F48,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I48" s="14" t="n">
         <v>46314</v>
@@ -6280,39 +6317,39 @@
       </c>
       <c r="L48" s="12"/>
       <c r="M48" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="N48" s="12" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="O48" s="4"/>
       <c r="P48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G49" s="13" t="str">
         <f aca="false">IF($F49="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F49,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I49" s="14" t="n">
         <v>46321</v>
@@ -6326,7 +6363,7 @@
       </c>
       <c r="L49" s="12"/>
       <c r="M49" s="4" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="N49" s="12"/>
       <c r="O49" s="4"/>
@@ -6334,29 +6371,29 @@
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G50" s="13" t="str">
         <f aca="false">IF($F50="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F50,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I50" s="14" t="n">
         <v>46307</v>
@@ -6369,7 +6406,7 @@
         <v>46318</v>
       </c>
       <c r="L50" s="12" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="M50" s="4"/>
       <c r="N50" s="12"/>
@@ -6378,29 +6415,29 @@
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G51" s="13" t="str">
         <f aca="false">IF($F51="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F51,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I51" s="14" t="n">
         <v>46314</v>
@@ -6413,7 +6450,7 @@
         <v>46339</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="M51" s="4"/>
       <c r="N51" s="12"/>
@@ -6422,29 +6459,29 @@
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G52" s="13" t="str">
         <f aca="false">IF($F52="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F52,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I52" s="14" t="n">
         <v>46328</v>
@@ -6457,40 +6494,40 @@
         <v>46353</v>
       </c>
       <c r="L52" s="12" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="M52" s="4"/>
       <c r="N52" s="12"/>
       <c r="O52" s="4"/>
       <c r="P52" s="12" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G53" s="13" t="str">
         <f aca="false">IF($F53="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F53,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I53" s="14" t="n">
         <v>46202</v>
@@ -6507,34 +6544,34 @@
       <c r="N53" s="12"/>
       <c r="O53" s="4"/>
       <c r="P53" s="12" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G54" s="13" t="str">
         <f aca="false">IF($F54="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F54,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>46202</v>
@@ -6551,34 +6588,34 @@
       <c r="N54" s="12"/>
       <c r="O54" s="4"/>
       <c r="P54" s="12" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G55" s="13" t="str">
         <f aca="false">IF($F55="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F55,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>46349</v>
@@ -6591,10 +6628,10 @@
         <v>46360</v>
       </c>
       <c r="L55" s="12" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="N55" s="12"/>
       <c r="O55" s="4"/>
@@ -6602,29 +6639,29 @@
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G56" s="13" t="str">
         <f aca="false">IF($F56="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F56,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>46356</v>
@@ -6637,7 +6674,7 @@
         <v>46381</v>
       </c>
       <c r="L56" s="12" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="M56" s="4"/>
       <c r="N56" s="12"/>
@@ -6646,29 +6683,29 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G57" s="13" t="str">
         <f aca="false">IF($F57="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F57,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>46377</v>
@@ -6681,7 +6718,7 @@
         <v>46388</v>
       </c>
       <c r="L57" s="12" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M57" s="4"/>
       <c r="N57" s="12"/>
@@ -6690,29 +6727,29 @@
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G58" s="13" t="str">
         <f aca="false">IF($F58="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F58,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I58" s="14" t="n">
         <v>46307</v>
@@ -6732,29 +6769,29 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G59" s="13" t="str">
         <f aca="false">IF($F59="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F59,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I59" s="14" t="n">
         <v>46328</v>
@@ -6767,42 +6804,42 @@
         <v>46353</v>
       </c>
       <c r="L59" s="12" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M59" s="4"/>
       <c r="N59" s="12"/>
       <c r="O59" s="4" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="P59" s="12" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G60" s="13" t="str">
         <f aca="false">IF($F60="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F60,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I60" s="14" t="n">
         <v>46209</v>
@@ -6819,34 +6856,34 @@
       <c r="N60" s="12"/>
       <c r="O60" s="4"/>
       <c r="P60" s="12" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G61" s="13" t="str">
         <f aca="false">IF($F61="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F61,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I61" s="14" t="n">
         <v>46209</v>
@@ -6863,34 +6900,34 @@
       <c r="N61" s="12"/>
       <c r="O61" s="4"/>
       <c r="P61" s="12" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G62" s="13" t="str">
         <f aca="false">IF($F62="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F62,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I62" s="14" t="n">
         <v>46335</v>
@@ -6903,7 +6940,7 @@
         <v>46360</v>
       </c>
       <c r="L62" s="12" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="M62" s="4"/>
       <c r="N62" s="12"/>
@@ -6912,29 +6949,29 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G63" s="13" t="str">
         <f aca="false">IF($F63="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F63,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I63" s="14" t="n">
         <v>46356</v>
@@ -6947,40 +6984,40 @@
         <v>46381</v>
       </c>
       <c r="L63" s="12" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="M63" s="4"/>
       <c r="N63" s="12"/>
       <c r="O63" s="4"/>
       <c r="P63" s="12" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G64" s="13" t="str">
         <f aca="false">IF($F64="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F64,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I64" s="14" t="n">
         <v>46223</v>
@@ -6997,34 +7034,34 @@
       <c r="N64" s="12"/>
       <c r="O64" s="4"/>
       <c r="P64" s="12" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G65" s="13" t="str">
         <f aca="false">IF($F65="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F65,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I65" s="14" t="n">
         <v>46370</v>
@@ -7037,7 +7074,7 @@
         <v>46388</v>
       </c>
       <c r="L65" s="12" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M65" s="4"/>
       <c r="N65" s="12"/>
@@ -7046,29 +7083,29 @@
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G66" s="13" t="str">
         <f aca="false">IF($F66="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F66,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I66" s="14" t="n">
         <v>46223</v>
@@ -7085,34 +7122,34 @@
       <c r="N66" s="12"/>
       <c r="O66" s="4"/>
       <c r="P66" s="12" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G67" s="13" t="str">
         <f aca="false">IF($F67="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F67,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I67" s="14" t="n">
         <v>46370</v>
@@ -7125,7 +7162,7 @@
         <v>46388</v>
       </c>
       <c r="L67" s="12" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="M67" s="4"/>
       <c r="N67" s="12"/>
@@ -7134,29 +7171,29 @@
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G68" s="13" t="str">
         <f aca="false">IF($F68="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F68,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I68" s="14" t="n">
         <v>46349</v>
@@ -7169,10 +7206,10 @@
         <v>46374</v>
       </c>
       <c r="L68" s="12" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="N68" s="12"/>
       <c r="O68" s="4"/>
@@ -7180,29 +7217,29 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G69" s="13" t="str">
         <f aca="false">IF($F69="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F69,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I69" s="14" t="n">
         <v>46307</v>
@@ -7215,7 +7252,7 @@
         <v>46325</v>
       </c>
       <c r="L69" s="12" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="M69" s="4"/>
       <c r="N69" s="12"/>
@@ -7224,29 +7261,29 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G70" s="13" t="str">
         <f aca="false">IF($F70="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F70,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I70" s="14" t="n">
         <v>46321</v>
@@ -7259,7 +7296,7 @@
         <v>46339</v>
       </c>
       <c r="L70" s="12" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M70" s="4"/>
       <c r="N70" s="12"/>
@@ -7268,29 +7305,29 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G71" s="13" t="str">
         <f aca="false">IF($F71="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F71,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I71" s="14" t="n">
         <v>46335</v>
@@ -7303,7 +7340,7 @@
         <v>46353</v>
       </c>
       <c r="L71" s="12" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="M71" s="4"/>
       <c r="N71" s="12"/>
@@ -7312,29 +7349,29 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G72" s="13" t="str">
         <f aca="false">IF($F72="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F72,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I72" s="14" t="n">
         <v>46328</v>
@@ -7347,7 +7384,7 @@
         <v>46346</v>
       </c>
       <c r="L72" s="12" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="M72" s="4"/>
       <c r="N72" s="12"/>
@@ -7356,29 +7393,29 @@
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G73" s="13" t="str">
         <f aca="false">IF($F73="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F73,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I73" s="14" t="n">
         <v>46349</v>
@@ -7391,7 +7428,7 @@
         <v>46367</v>
       </c>
       <c r="L73" s="12" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="M73" s="4"/>
       <c r="N73" s="12"/>
@@ -7400,29 +7437,29 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G74" s="13" t="str">
         <f aca="false">IF($F74="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F74,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I74" s="14" t="n">
         <v>46370</v>
@@ -7435,7 +7472,7 @@
         <v>46388</v>
       </c>
       <c r="L74" s="12" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M74" s="4"/>
       <c r="N74" s="12"/>
@@ -7444,29 +7481,29 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G75" s="13" t="str">
         <f aca="false">IF($F75="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F75,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I75" s="14" t="n">
         <v>46391</v>
@@ -7479,7 +7516,7 @@
         <v>46402</v>
       </c>
       <c r="L75" s="12" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="M75" s="4"/>
       <c r="N75" s="12"/>
@@ -7488,29 +7525,29 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G76" s="13" t="str">
         <f aca="false">IF($F76="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F76,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I76" s="14" t="n">
         <v>46356</v>
@@ -7523,7 +7560,7 @@
         <v>46367</v>
       </c>
       <c r="L76" s="12" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M76" s="4"/>
       <c r="N76" s="12"/>
@@ -7532,27 +7569,27 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G77" s="13" t="str">
         <f aca="false">IF($F77="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F77,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I77" s="14" t="n">
         <v>46363</v>
@@ -7565,7 +7602,7 @@
         <v>46374</v>
       </c>
       <c r="L77" s="12" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="M77" s="4"/>
       <c r="N77" s="12"/>
@@ -7574,27 +7611,27 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G78" s="13" t="str">
         <f aca="false">IF($F78="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F78,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I78" s="14" t="n">
         <v>46370</v>
@@ -7607,7 +7644,7 @@
         <v>46388</v>
       </c>
       <c r="L78" s="12" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="M78" s="4"/>
       <c r="N78" s="12"/>
@@ -7616,29 +7653,29 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G79" s="13" t="str">
         <f aca="false">IF($F79="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F79,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I79" s="14" t="n">
         <v>46384</v>
@@ -7651,7 +7688,7 @@
         <v>46395</v>
       </c>
       <c r="L79" s="12" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="M79" s="4"/>
       <c r="N79" s="12"/>
@@ -7660,29 +7697,29 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G80" s="13" t="str">
         <f aca="false">IF($F80="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F80,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I80" s="14" t="n">
         <v>46391</v>
@@ -7695,7 +7732,7 @@
         <v>46409</v>
       </c>
       <c r="L80" s="12" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="M80" s="4"/>
       <c r="N80" s="12"/>
@@ -7704,29 +7741,29 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G81" s="13" t="str">
         <f aca="false">IF($F81="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F81,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I81" s="14" t="n">
         <v>46349</v>
@@ -7739,7 +7776,7 @@
         <v>46353</v>
       </c>
       <c r="L81" s="12" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="M81" s="4"/>
       <c r="N81" s="12"/>
@@ -7748,29 +7785,29 @@
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G82" s="13" t="str">
         <f aca="false">IF($F82="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F82,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I82" s="14" t="n">
         <v>46363</v>
@@ -7783,7 +7820,7 @@
         <v>46367</v>
       </c>
       <c r="L82" s="12" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="M82" s="4"/>
       <c r="N82" s="12"/>
@@ -7792,29 +7829,29 @@
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G83" s="13" t="str">
         <f aca="false">IF($F83="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F83,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I83" s="14" t="n">
         <v>46391</v>
@@ -7827,7 +7864,7 @@
         <v>46395</v>
       </c>
       <c r="L83" s="12" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="M83" s="4"/>
       <c r="N83" s="12"/>
@@ -7836,29 +7873,29 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G84" s="13" t="str">
         <f aca="false">IF($F84="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F84,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I84" s="14" t="n">
         <v>46391</v>
@@ -7871,7 +7908,7 @@
         <v>46395</v>
       </c>
       <c r="L84" s="12" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="M84" s="4"/>
       <c r="N84" s="12"/>
@@ -7880,29 +7917,29 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G85" s="13" t="str">
         <f aca="false">IF($F85="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F85,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I85" s="14" t="n">
         <v>46398</v>
@@ -7915,7 +7952,7 @@
         <v>46402</v>
       </c>
       <c r="L85" s="12" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="M85" s="4"/>
       <c r="N85" s="12"/>
@@ -7924,29 +7961,29 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G86" s="13" t="str">
         <f aca="false">IF($F86="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F86,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I86" s="14" t="n">
         <v>46405</v>
@@ -7959,7 +7996,7 @@
         <v>46409</v>
       </c>
       <c r="L86" s="12" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M86" s="4"/>
       <c r="N86" s="12"/>
@@ -7968,29 +8005,29 @@
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G87" s="13" t="str">
         <f aca="false">IF($F87="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F87,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I87" s="14" t="n">
         <v>46195</v>
@@ -8007,34 +8044,34 @@
       <c r="N87" s="12"/>
       <c r="O87" s="4"/>
       <c r="P87" s="12" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G88" s="13" t="str">
         <f aca="false">IF($F88="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F88,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I88" s="14" t="n">
         <v>46195</v>
@@ -8051,34 +8088,34 @@
       <c r="N88" s="12"/>
       <c r="O88" s="4"/>
       <c r="P88" s="12" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G89" s="13" t="str">
         <f aca="false">IF($F89="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F89,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I89" s="14" t="n">
         <v>46195</v>
@@ -8095,34 +8132,34 @@
       <c r="N89" s="12"/>
       <c r="O89" s="4"/>
       <c r="P89" s="12" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="F90" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G90" s="13" t="str">
         <f aca="false">IF($F90="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F90,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I90" s="14" t="n">
         <v>46195</v>
@@ -8139,34 +8176,34 @@
       <c r="N90" s="12"/>
       <c r="O90" s="4"/>
       <c r="P90" s="12" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G91" s="13" t="str">
         <f aca="false">IF($F91="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F91,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I91" s="14" t="n">
         <v>46195</v>
@@ -8183,34 +8220,34 @@
       <c r="N91" s="12"/>
       <c r="O91" s="4"/>
       <c r="P91" s="12" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G92" s="13" t="str">
         <f aca="false">IF($F92="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F92,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I92" s="14" t="n">
         <v>46195</v>
@@ -8227,34 +8264,34 @@
       <c r="N92" s="12"/>
       <c r="O92" s="4"/>
       <c r="P92" s="12" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G93" s="13" t="str">
         <f aca="false">IF($F93="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F93,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I93" s="14" t="n">
         <v>46195</v>
@@ -8271,34 +8308,34 @@
       <c r="N93" s="12"/>
       <c r="O93" s="4"/>
       <c r="P93" s="12" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G94" s="13" t="str">
         <f aca="false">IF($F94="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F94,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I94" s="14" t="n">
         <v>46195</v>
@@ -8315,34 +8352,34 @@
       <c r="N94" s="12"/>
       <c r="O94" s="4"/>
       <c r="P94" s="12" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G95" s="13" t="str">
         <f aca="false">IF($F95="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F95,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I95" s="14" t="n">
         <v>46195</v>
@@ -8359,34 +8396,34 @@
       <c r="N95" s="12"/>
       <c r="O95" s="4"/>
       <c r="P95" s="12" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G96" s="13" t="str">
         <f aca="false">IF($F96="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F96,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I96" s="14" t="n">
         <v>46195</v>
@@ -8403,34 +8440,34 @@
       <c r="N96" s="12"/>
       <c r="O96" s="4"/>
       <c r="P96" s="12" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G97" s="13" t="str">
         <f aca="false">IF($F97="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F97,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I97" s="14" t="n">
         <v>46195</v>
@@ -8447,34 +8484,34 @@
       <c r="N97" s="12"/>
       <c r="O97" s="4"/>
       <c r="P97" s="12" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G98" s="13" t="str">
         <f aca="false">IF($F98="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F98,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I98" s="14" t="n">
         <v>46195</v>
@@ -8491,34 +8528,34 @@
       <c r="N98" s="12"/>
       <c r="O98" s="4"/>
       <c r="P98" s="12" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G99" s="13" t="str">
         <f aca="false">IF($F99="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F99,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I99" s="14" t="n">
         <v>46202</v>
@@ -8535,34 +8572,34 @@
       <c r="N99" s="12"/>
       <c r="O99" s="4"/>
       <c r="P99" s="12" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G100" s="13" t="str">
         <f aca="false">IF($F100="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F100,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I100" s="14" t="n">
         <v>46202</v>
@@ -8579,34 +8616,34 @@
       <c r="N100" s="12"/>
       <c r="O100" s="4"/>
       <c r="P100" s="12" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="12" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G101" s="13" t="str">
         <f aca="false">IF($F101="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F101,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I101" s="14" t="n">
         <v>46202</v>
@@ -8623,34 +8660,34 @@
       <c r="N101" s="12"/>
       <c r="O101" s="4"/>
       <c r="P101" s="12" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="12" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F102" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G102" s="13" t="str">
         <f aca="false">IF($F102="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F102,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I102" s="14" t="n">
         <v>46209</v>
@@ -8667,34 +8704,34 @@
       <c r="N102" s="12"/>
       <c r="O102" s="4"/>
       <c r="P102" s="12" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="12" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G103" s="13" t="str">
         <f aca="false">IF($F103="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F103,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I103" s="14" t="n">
         <v>46216</v>
@@ -8711,34 +8748,34 @@
       <c r="N103" s="12"/>
       <c r="O103" s="4"/>
       <c r="P103" s="12" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="12" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G104" s="13" t="str">
         <f aca="false">IF($F104="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F104,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I104" s="14" t="n">
         <v>46216</v>
@@ -8755,34 +8792,34 @@
       <c r="N104" s="12"/>
       <c r="O104" s="4"/>
       <c r="P104" s="12" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="12" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G105" s="13" t="str">
         <f aca="false">IF($F105="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F105,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I105" s="14" t="n">
         <v>46216</v>
@@ -8799,34 +8836,34 @@
       <c r="N105" s="12"/>
       <c r="O105" s="4"/>
       <c r="P105" s="12" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="12" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G106" s="13" t="str">
         <f aca="false">IF($F106="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F106,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I106" s="14" t="n">
         <v>46223</v>
@@ -8843,34 +8880,34 @@
       <c r="N106" s="12"/>
       <c r="O106" s="4"/>
       <c r="P106" s="12" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="12" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G107" s="13" t="str">
         <f aca="false">IF($F107="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F107,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I107" s="14" t="n">
         <v>46223</v>
@@ -8887,34 +8924,34 @@
       <c r="N107" s="12"/>
       <c r="O107" s="4"/>
       <c r="P107" s="12" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="12" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G108" s="13" t="str">
         <f aca="false">IF($F108="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F108,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I108" s="14" t="n">
         <v>46230</v>
@@ -8931,34 +8968,34 @@
       <c r="N108" s="12"/>
       <c r="O108" s="4"/>
       <c r="P108" s="12" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="12" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G109" s="13" t="str">
         <f aca="false">IF($F109="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F109,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I109" s="14" t="n">
         <v>46195</v>
@@ -8975,34 +9012,34 @@
       <c r="N109" s="12"/>
       <c r="O109" s="4"/>
       <c r="P109" s="12" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="12" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G110" s="13" t="str">
         <f aca="false">IF($F110="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F110,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I110" s="14" t="n">
         <v>46195</v>
@@ -9019,34 +9056,34 @@
       <c r="N110" s="12"/>
       <c r="O110" s="4"/>
       <c r="P110" s="12" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="12" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G111" s="13" t="str">
         <f aca="false">IF($F111="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F111,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I111" s="14" t="n">
         <v>46202</v>
@@ -9063,34 +9100,34 @@
       <c r="N111" s="12"/>
       <c r="O111" s="4"/>
       <c r="P111" s="12" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="12" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G112" s="13" t="str">
         <f aca="false">IF($F112="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F112,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I112" s="14" t="n">
         <v>46209</v>
@@ -9107,34 +9144,34 @@
       <c r="N112" s="12"/>
       <c r="O112" s="4"/>
       <c r="P112" s="12" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="12" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G113" s="13" t="str">
         <f aca="false">IF($F113="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F113,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I113" s="14" t="n">
         <v>46209</v>
@@ -9151,34 +9188,34 @@
       <c r="N113" s="12"/>
       <c r="O113" s="4"/>
       <c r="P113" s="12" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="12" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G114" s="13" t="str">
         <f aca="false">IF($F114="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F114,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I114" s="14" t="n">
         <v>46216</v>
@@ -9195,34 +9232,34 @@
       <c r="N114" s="12"/>
       <c r="O114" s="4"/>
       <c r="P114" s="12" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="12" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G115" s="13" t="str">
         <f aca="false">IF($F115="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F115,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I115" s="14"/>
       <c r="J115" s="12"/>
@@ -9234,37 +9271,37 @@
       <c r="M115" s="4"/>
       <c r="N115" s="12"/>
       <c r="O115" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P115" s="12" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="12" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="F116" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G116" s="13" t="str">
         <f aca="false">IF($F116="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F116,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I116" s="14"/>
       <c r="J116" s="12"/>
@@ -9276,37 +9313,37 @@
       <c r="M116" s="4"/>
       <c r="N116" s="12"/>
       <c r="O116" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P116" s="12" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="12" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G117" s="13" t="str">
         <f aca="false">IF($F117="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F117,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="12"/>
@@ -9318,37 +9355,37 @@
       <c r="M117" s="4"/>
       <c r="N117" s="12"/>
       <c r="O117" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="12" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F118" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G118" s="13" t="str">
         <f aca="false">IF($F118="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F118,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I118" s="14"/>
       <c r="J118" s="12"/>
@@ -9360,37 +9397,37 @@
       <c r="M118" s="4"/>
       <c r="N118" s="12"/>
       <c r="O118" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P118" s="12" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="12" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G119" s="13" t="str">
         <f aca="false">IF($F119="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F119,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I119" s="14"/>
       <c r="J119" s="12"/>
@@ -9402,37 +9439,37 @@
       <c r="M119" s="4"/>
       <c r="N119" s="12"/>
       <c r="O119" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="12" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F120" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G120" s="13" t="str">
         <f aca="false">IF($F120="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F120,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="12"/>
@@ -9444,37 +9481,37 @@
       <c r="M120" s="4"/>
       <c r="N120" s="12"/>
       <c r="O120" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="12" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G121" s="13" t="str">
         <f aca="false">IF($F121="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F121,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I121" s="14"/>
       <c r="J121" s="12"/>
@@ -9486,37 +9523,37 @@
       <c r="M121" s="4"/>
       <c r="N121" s="12"/>
       <c r="O121" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="12" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="F122" s="12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G122" s="13" t="str">
         <f aca="false">IF($F122="","",IFERROR(INDEX(Lists!$B$4:$B$12,MATCH($F122,Lists!$A$4:$A$12,0)),""))</f>
         <v>TBD</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="12"/>
@@ -9528,10 +9565,10 @@
       <c r="M122" s="4"/>
       <c r="N122" s="12"/>
       <c r="O122" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16297,27 +16334,27 @@
       <formula>H4="Partially Completed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:P403">
+  <conditionalFormatting sqref="K4:K403">
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>AND($A4&lt;&gt;"",ISERROR(FIND(".",$A4)))</formula>
+      <formula>AND(ISNUMBER($K4),$K4&lt;TODAY(),$H4&lt;&gt;"Complete")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K403">
+  <conditionalFormatting sqref="A4:G403 I4:P403">
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>AND(ISNUMBER($K4),$K4&lt;TODAY(),$H4&lt;&gt;"Complete")</formula>
+      <formula>AND($A4&lt;&gt;"",ISERROR(FIND(".",$A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H403" type="list">
-      <formula1>Lists!$E$4:$E$8</formula1>
+      <formula1>"Not Started,In Progress,Blocked,Complete,Partially Completed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B4:B403" type="list">
-      <formula1>Lists!$F$4:$F$8</formula1>
+      <formula1>"G1 ED305 live digital twin,G2 SCooP dataset &amp; paper,Shared SCooP testbed,Dual-Link Communication,Semantic Communication"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F4:F403" type="list">
-      <formula1>Lists!$A$4:$A$12</formula1>
+      <formula1>"Sensors &amp; platform,GS-SLAM,Scene detection,Isaac Sim,Sionna RT,SCooP dataset,Dual-link comms,Semantic comms,All (integration)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J4:J403" type="whole">
@@ -16362,14 +16399,14 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17" t="n">
         <v>46195</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="F2" s="18" t="n">
         <f aca="true">TODAY()</f>
@@ -16378,22 +16415,22 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G4" s="20" t="n">
         <f aca="false">$C$2+7*0</f>
@@ -16572,7 +16609,7 @@
         <v>46496</v>
       </c>
       <c r="BA4" s="5" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16646,7 +16683,7 @@
       <c r="AX5" s="23"/>
       <c r="AZ5" s="24"/>
       <c r="BA5" s="21" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16720,7 +16757,7 @@
       <c r="AX6" s="23"/>
       <c r="AZ6" s="25"/>
       <c r="BA6" s="21" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16794,7 +16831,7 @@
       <c r="AX7" s="23"/>
       <c r="AZ7" s="26"/>
       <c r="BA7" s="21" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16868,7 +16905,7 @@
       <c r="AX8" s="23"/>
       <c r="AZ8" s="27"/>
       <c r="BA8" s="21" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16942,7 +16979,7 @@
       <c r="AX9" s="23"/>
       <c r="AZ9" s="28"/>
       <c r="BA9" s="21" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17016,7 +17053,7 @@
       <c r="AX10" s="23"/>
       <c r="AZ10" s="29"/>
       <c r="BA10" s="21" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17090,7 +17127,7 @@
       <c r="AX11" s="23"/>
       <c r="AZ11" s="30"/>
       <c r="BA11" s="21" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17233,7 +17270,7 @@
       <c r="AW13" s="23"/>
       <c r="AX13" s="23"/>
       <c r="BA13" s="31" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44615,22 +44652,22 @@
       <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),ISNUMBER(SEARCH("-M",$A5)))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="Complete")</formula>
+      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="Complete",NOT(ISNUMBER(SEARCH("-M",$A5))))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
-      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="In Progress")</formula>
+      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="In Progress",NOT(ISNUMBER(SEARCH("-M",$A5))))</formula>
     </cfRule>
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
-      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="Partially Completed")</formula>
+      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="Partially Completed",NOT(ISNUMBER(SEARCH("-M",$A5))))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
-      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="Blocked")</formula>
+      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),$D5="Blocked",NOT(ISNUMBER(SEARCH("-M",$A5))))</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
-      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),OR($D5="Not Started",$D5=""))</formula>
+      <formula>AND(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5),OR($D5="Not Started",$D5=""),NOT(ISNUMBER(SEARCH("-M",$A5))))</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
-      <formula>AND(G$4&lt;=TODAY(),G$4+6&gt;=TODAY())</formula>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>AND(AND(G$4&lt;=TODAY(),G$4+6&gt;=TODAY()),NOT(AND(ISNUMBER($E5),ISNUMBER($F5),G$4&lt;=$F5,G$4+6&gt;=$E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:AX4">
@@ -44655,14 +44692,14 @@
       <formula>D5="Partially Completed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:F404">
+  <conditionalFormatting sqref="F5:F404">
     <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>AND($A5&lt;&gt;"",ISERROR(FIND(".",$A5)))</formula>
+      <formula>AND(ISNUMBER($F5),$F5&lt;TODAY(),$D5&lt;&gt;"Complete")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F404">
+  <conditionalFormatting sqref="A5:C404 E5:F404">
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>AND(ISNUMBER($F5),$F5&lt;TODAY(),$D5&lt;&gt;"Complete")</formula>
+      <formula>AND($A5&lt;&gt;"",ISERROR(FIND(".",$A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -44705,191 +44742,191 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B4" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="L4" s="33"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B5" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="L5" s="33"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B6" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="L6" s="33"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B7" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -44898,34 +44935,34 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B8" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="33"/>
@@ -44933,31 +44970,31 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B9" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -44966,148 +45003,148 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B10" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="L10" s="33"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B11" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="L11" s="33"/>
       <c r="M11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="B12" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="L12" s="33"/>
       <c r="M12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B13" s="33" t="n">
         <v>46302</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="L13" s="33"/>
       <c r="M13" s="4"/>
@@ -47975,26 +48012,26 @@
       <formula>F4="Minor"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:M203">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+  <conditionalFormatting sqref="A4:E203 G4:M203">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>OR($G4="Resolved",$G4="Won't fix")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4:C203" type="list">
-      <formula1>Lists!$F$4:$F$8</formula1>
+      <formula1>"G1 ED305 live digital twin,G2 SCooP dataset &amp; paper,Shared SCooP testbed,Dual-Link Communication,Semantic Communication"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E4:E203" type="list">
-      <formula1>Lists!$A$4:$A$12</formula1>
+      <formula1>"Sensors &amp; platform,GS-SLAM,Scene detection,Isaac Sim,Sionna RT,SCooP dataset,Dual-link comms,Semantic comms,All (integration)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F4:F203" type="list">
-      <formula1>Lists!$G$4:$G$6</formula1>
+      <formula1>"Blocker,Major,Minor"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G4:G203" type="list">
-      <formula1>Lists!$H$4:$H$7</formula1>
+      <formula1>"Open,Investigating,Resolved,Won't fix"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -48035,503 +48072,503 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>628</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>631</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K17" s="4"/>
     </row>
@@ -49661,7 +49698,7 @@
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>J4="Defined"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>J4="Implemented"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
@@ -49670,15 +49707,15 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H103" type="list">
-      <formula1>Lists!$A$4:$A$12</formula1>
+      <formula1>"Sensors &amp; platform,GS-SLAM,Scene detection,Isaac Sim,Sionna RT,SCooP dataset,Dual-link comms,Semantic comms,All (integration)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I4:I103" type="list">
-      <formula1>Lists!$A$4:$A$12</formula1>
+      <formula1>"Sensors &amp; platform,GS-SLAM,Scene detection,Isaac Sim,Sionna RT,SCooP dataset,Dual-link comms,Semantic comms,All (integration)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J4:J103" type="list">
-      <formula1>Lists!$I$4:$I$7</formula1>
+      <formula1>"Not defined,Defined,Implemented,Tested"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -49714,27 +49751,27 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49742,19 +49779,19 @@
         <v>46300</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53785,71 +53822,71 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="35" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B4" s="34" t="n">
         <v>46301</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59843,7 +59880,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C503" type="list">
-      <formula1>Lists!$F$4:$F$8</formula1>
+      <formula1>"G1 ED305 live digital twin,G2 SCooP dataset &amp; paper,Shared SCooP testbed,Dual-Link Communication,Semantic Communication"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -59877,195 +59914,195 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>638</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="36" t="s">
-        <v>631</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="G4" s="8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>638</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>631</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="G5" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>638</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>631</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="G6" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>638</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="36" t="s">
-        <v>631</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>638</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>631</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>709</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
